--- a/data/rental_properties_assignment_ready.xlsx
+++ b/data/rental_properties_assignment_ready.xlsx
@@ -2,8 +2,8 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Properties" sheetId="1" r:id="Re5ca1de7a0b849e8"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data notes" sheetId="2" r:id="Ra17248a28e254ca3"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Properties" sheetId="1" r:id="R537ea555a69449fd"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Data notes" sheetId="2" r:id="R7d080be4a0c944a9"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -46,7 +46,7 @@
   <x:cellStyleXfs count="1">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="9">
+  <x:cellXfs count="10">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <x:xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -62,6 +62,7 @@
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment wrapText="1"/>
     </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </x:cellXfs>
   <x:cellStyles count="1">
     <x:cellStyle name="Normal" xfId="0"/>
@@ -294,6 +295,7 @@
     <x:col min="28" max="28" width="34" hidden="0" customWidth="1"/>
     <x:col min="29" max="29" width="34" hidden="0" customWidth="1"/>
     <x:col min="30" max="30" width="34" hidden="0" customWidth="1"/>
+    <x:col min="31" max="31" width="68" hidden="0" customWidth="1"/>
   </x:cols>
   <x:sheetData>
     <x:row r="1" ht="28" customHeight="1">
@@ -387,8 +389,11 @@
       <x:c r="AD1" s="4" t="str">
         <x:v>coordinate_provenance</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2">
+      <x:c r="AE1" t="str">
+        <x:v>property_description</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" ht="76" customHeight="1">
       <x:c r="A2" t="str">
         <x:v>BC-1000001</x:v>
       </x:c>
@@ -479,8 +484,11 @@
       <x:c r="AD2" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="3">
+      <x:c r="AE2" s="8" t="str">
+        <x:v>Shinjuku Grand Resort is a resort listing in Shinjuku, Tokyo, Japan with two bedrooms and two bathrooms. The property is listed as child-friendly and includes a pool. Breakfast is also listed as included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" ht="76" customHeight="1">
       <x:c r="A3" t="str">
         <x:v>BC-1000002</x:v>
       </x:c>
@@ -571,8 +579,11 @@
       <x:c r="AD3" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="4">
+      <x:c r="AE3" s="8" t="str">
+        <x:v>Based in Shibuya, Tokyo, Japan, Shibuya Riverside Resort is listed as a resort with three bedrooms and one bathroom. Breakfast is listed as included, and a gym offers an option to stay active. Additional amenities include internet access and parking.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" ht="76" customHeight="1">
       <x:c r="A4" t="str">
         <x:v>BC-1000003</x:v>
       </x:c>
@@ -663,8 +674,11 @@
       <x:c r="AD4" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="5">
+      <x:c r="AE4" s="8" t="str">
+        <x:v>In Namba, Osaka, Japan, Namba Central Hotel offers a hotel stay with five bedrooms and one bathroom. Wheelchair accessibility and a kitchen are among the listed conveniences. Other listed amenities include laundry facilities, child-friendly facilities, and air conditioning. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" ht="76" customHeight="1">
       <x:c r="A5" t="str">
         <x:v>BC-1000004</x:v>
       </x:c>
@@ -755,8 +769,11 @@
       <x:c r="AD5" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="6">
+      <x:c r="AE5" s="8" t="str">
+        <x:v>Umeda Garden House is a house in Umeda, Osaka, Japan, featuring two bedrooms and two bathrooms in its listed layout. Wheelchair accessibility and a kitchen are among the listed conveniences. Other listed amenities include parking, a hot tub, a pool, and laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" ht="76" customHeight="1">
       <x:c r="A6" t="str">
         <x:v>BC-1000005</x:v>
       </x:c>
@@ -847,8 +864,11 @@
       <x:c r="AD6" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="7">
+      <x:c r="AE6" s="8" t="str">
+        <x:v>For a hotel stay in Gion, Kyoto, Japan, The Gion Hotel has one bedroom and two bathrooms. The property is listed as child-friendly and includes a pool. Other listed amenities include a kitchen, a gym, and pet-friendly accommodation. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" ht="76" customHeight="1">
       <x:c r="A7" t="str">
         <x:v>BC-1000006</x:v>
       </x:c>
@@ -939,8 +959,11 @@
       <x:c r="AD7" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="8">
+      <x:c r="AE7" s="8" t="str">
+        <x:v>Arashiyama Harbor Hostel is a hostel accommodation listed in Arashiyama, Kyoto, Japan. Its layout includes two bedrooms and three bathrooms. Its listed features include air conditioning and wheelchair accessibility. The listing also includes a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" ht="76" customHeight="1">
       <x:c r="A8" t="str">
         <x:v>BC-1000007</x:v>
       </x:c>
@@ -1031,8 +1054,11 @@
       <x:c r="AD8" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="9">
+      <x:c r="AE8" s="8" t="str">
+        <x:v>Nara Skyline Hostel is a hostel listing in Nara, Japan with three bedrooms and two bathrooms. Wheelchair accessibility and a kitchen are among the listed conveniences. Additional amenities include pet-friendly accommodation and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" ht="76" customHeight="1">
       <x:c r="A9" t="str">
         <x:v>BC-1000008</x:v>
       </x:c>
@@ -1123,8 +1149,11 @@
       <x:c r="AD9" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="10">
+      <x:c r="AE9" s="8" t="str">
+        <x:v>Based in Ichinomiya, Aichi, Japan, Ichinomiya House is listed as a house with three bedrooms and three bathrooms. A pool and hot tub provide options for relaxing between outings. Other listed amenities include laundry facilities. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" ht="76" customHeight="1">
       <x:c r="A10" t="str">
         <x:v>BC-1000009</x:v>
       </x:c>
@@ -1215,8 +1244,11 @@
       <x:c r="AD10" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="11">
+      <x:c r="AE10" s="8" t="str">
+        <x:v>In Nagoya, Aichi, Japan, Nagoya Grand Apartment offers an apartment stay with two bedrooms and two bathrooms. A gym and kitchen are listed among the property's amenities. Additional amenities include internet access and air conditioning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" ht="76" customHeight="1">
       <x:c r="A11" t="str">
         <x:v>BC-1000010</x:v>
       </x:c>
@@ -1307,8 +1339,11 @@
       <x:c r="AD11" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="12">
+      <x:c r="AE11" s="8" t="str">
+        <x:v>Sabae Riverside Resort is a resort in Sabae, Fukui, Japan, featuring four bedrooms and two bathrooms in its listed layout. Internet access and parking add everyday convenience. Additional amenities include child-friendly facilities and pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" ht="76" customHeight="1">
       <x:c r="A12" t="str">
         <x:v>BC-1000011</x:v>
       </x:c>
@@ -1399,8 +1434,11 @@
       <x:c r="AD12" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="13">
+      <x:c r="AE12" s="8" t="str">
+        <x:v>For a hostel stay in Fukui, Japan, Fukui Central Hostel has three bedrooms and two bathrooms. The property is listed as child-friendly and includes a pool. Other listed amenities include parking, a kitchen, and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" ht="76" customHeight="1">
       <x:c r="A13" t="str">
         <x:v>BC-1000012</x:v>
       </x:c>
@@ -1491,8 +1529,11 @@
       <x:c r="AD13" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="14">
+      <x:c r="AE13" s="8" t="str">
+        <x:v>Sapporo Garden Apartment is an apartment accommodation listed in Sapporo, Hokkaido, Japan. Its layout includes four bedrooms and one bathroom. A gym and kitchen are listed among the property's amenities. Additional amenities include child-friendly facilities and air conditioning. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" ht="76" customHeight="1">
       <x:c r="A14" t="str">
         <x:v>BC-1000013</x:v>
       </x:c>
@@ -1583,8 +1624,11 @@
       <x:c r="AD14" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="15">
+      <x:c r="AE14" s="8" t="str">
+        <x:v>The Hakodate Resort is a resort listing in Hakodate, Hokkaido, Japan with five bedrooms and two bathrooms. Its listed features include a hot tub and laundry facilities. Additional amenities include pet-friendly accommodation and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" ht="76" customHeight="1">
       <x:c r="A15" t="str">
         <x:v>BC-1000014</x:v>
       </x:c>
@@ -1675,8 +1719,11 @@
       <x:c r="AD15" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="16">
+      <x:c r="AE15" s="8" t="str">
+        <x:v>Based in Fukuoka, Japan, Fukuoka Harbor Apartment is listed as an apartment with five bedrooms and two bathrooms. A hot tub and gym give guests both relaxation and activity options. Other listed amenities include child-friendly facilities, pet-friendly accommodation, and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" ht="76" customHeight="1">
       <x:c r="A16" t="str">
         <x:v>BC-1000015</x:v>
       </x:c>
@@ -1767,8 +1814,11 @@
       <x:c r="AD16" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="17">
+      <x:c r="AE16" s="8" t="str">
+        <x:v>In Naha, Okinawa, Japan, Naha Skyline Hotel offers a hotel stay with one bedroom and three bathrooms. A gym and kitchen are listed among the property's amenities. Other listed amenities include child-friendly facilities, pet-friendly accommodation, and laundry facilities. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" ht="76" customHeight="1">
       <x:c r="A17" t="str">
         <x:v>BC-1000016</x:v>
       </x:c>
@@ -1859,8 +1909,11 @@
       <x:c r="AD17" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="18">
+      <x:c r="AE17" s="8" t="str">
+        <x:v>Hiroshima House is a house in Hiroshima, Japan, featuring four bedrooms and one bathroom in its listed layout. The property is listed as both child-friendly and pet-friendly. Additional amenities include laundry facilities and parking. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" ht="76" customHeight="1">
       <x:c r="A18" t="str">
         <x:v>BC-1000017</x:v>
       </x:c>
@@ -1951,8 +2004,11 @@
       <x:c r="AD18" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="19">
+      <x:c r="AE18" s="8" t="str">
+        <x:v>For a hostel stay in Yokohama, Kanagawa, Japan, Yokohama Grand Hostel has three bedrooms and two bathrooms. A kitchen and laundry facilities make everyday routines more convenient. Additional amenities include air conditioning and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" ht="76" customHeight="1">
       <x:c r="A19" t="str">
         <x:v>BC-1000018</x:v>
       </x:c>
@@ -2043,8 +2099,11 @@
       <x:c r="AD19" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="20">
+      <x:c r="AE19" s="8" t="str">
+        <x:v>Kobe Riverside Villa is a villa accommodation listed in Kobe, Hyogo, Japan. Its layout includes two bedrooms and one bathroom. Breakfast is listed as included, alongside internet access. Additional amenities include wheelchair accessibility and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" ht="76" customHeight="1">
       <x:c r="A20" t="str">
         <x:v>BC-1000019</x:v>
       </x:c>
@@ -2135,8 +2194,11 @@
       <x:c r="AD20" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="21">
+      <x:c r="AE20" s="8" t="str">
+        <x:v>Sendai Central Hostel is a hostel listing in Sendai, Miyagi, Japan with five bedrooms and one bathroom. Its listed features include a pool and pet-friendly accommodation. The listing also includes wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" ht="76" customHeight="1">
       <x:c r="A21" t="str">
         <x:v>BC-1000020</x:v>
       </x:c>
@@ -2227,8 +2289,11 @@
       <x:c r="AD21" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="22">
+      <x:c r="AE21" s="8" t="str">
+        <x:v>Based in Kanazawa, Ishikawa, Japan, Kanazawa Garden Apartment is listed as an apartment with four bedrooms and one bathroom. Air conditioning and internet access are among the listed comforts. The listing also includes parking.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" ht="76" customHeight="1">
       <x:c r="A22" t="str">
         <x:v>BC-1000021</x:v>
       </x:c>
@@ -2319,8 +2384,11 @@
       <x:c r="AD22" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="23">
+      <x:c r="AE22" s="8" t="str">
+        <x:v>In Nagano, Japan, The Nagano Hotel offers a hotel stay with two bedrooms and one bathroom. A pool and hot tub provide options for relaxing between outings. Other listed amenities include wheelchair accessibility, a gym, and child-friendly facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" ht="76" customHeight="1">
       <x:c r="A23" t="str">
         <x:v>BC-1000022</x:v>
       </x:c>
@@ -2411,8 +2479,11 @@
       <x:c r="AD23" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="24">
+      <x:c r="AE23" s="8" t="str">
+        <x:v>Kumamoto Harbor House is a house in Kumamoto, Japan, featuring three bedrooms and two bathrooms in its listed layout. Internet access and parking add everyday convenience. Additional amenities include a kitchen and child-friendly facilities. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="76" customHeight="1">
       <x:c r="A24" t="str">
         <x:v>BC-1000023</x:v>
       </x:c>
@@ -2503,8 +2574,11 @@
       <x:c r="AD24" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="25">
+      <x:c r="AE24" s="8" t="str">
+        <x:v>For an apartment stay in Shizuoka, Japan, Shizuoka Skyline Apartment has three bedrooms and two bathrooms. A kitchen and internet access make it easier to maintain everyday routines. The listing also includes child-friendly facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" ht="76" customHeight="1">
       <x:c r="A25" t="str">
         <x:v>BC-1000024</x:v>
       </x:c>
@@ -2595,8 +2669,11 @@
       <x:c r="AD25" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="26">
+      <x:c r="AE25" s="8" t="str">
+        <x:v>Takayama Apartment is an apartment accommodation listed in Takayama, Gifu, Japan. Its layout includes one bedroom and three bathrooms. A hot tub and air conditioning are among the advertised comforts. Other listed amenities include a gym, parking, and laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" ht="76" customHeight="1">
       <x:c r="A26" t="str">
         <x:v>BC-1000025</x:v>
       </x:c>
@@ -2687,8 +2764,11 @@
       <x:c r="AD26" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="27">
+      <x:c r="AE26" s="8" t="str">
+        <x:v>Kawaguchiko Grand Apartment is an apartment listing in Kawaguchiko, Yamanashi, Japan with one bedroom and two bathrooms. With breakfast included and a kitchen, guests have practical choices for meals. The listing also includes pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" ht="76" customHeight="1">
       <x:c r="A27" t="str">
         <x:v>HA-2000001</x:v>
       </x:c>
@@ -2779,8 +2859,11 @@
       <x:c r="AD27" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="28">
+      <x:c r="AE27" s="8" t="str">
+        <x:v>Based in New York, United States, New York Grand Hotel is listed as a hotel with two bedrooms and three bathrooms. The property is listed as pet-friendly and includes parking. Additional amenities include wheelchair accessibility and laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" ht="76" customHeight="1">
       <x:c r="A28" t="str">
         <x:v>HA-2000002</x:v>
       </x:c>
@@ -2871,8 +2954,11 @@
       <x:c r="AD28" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="29">
+      <x:c r="AE28" s="8" t="str">
+        <x:v>In Los Angeles, California, United States, Los Angeles Riverside Hotel offers a hotel stay with three bedrooms and three bathrooms. With breakfast included and a kitchen, guests have practical choices for meals. Additional amenities include a hot tub and pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" ht="76" customHeight="1">
       <x:c r="A29" t="str">
         <x:v>HA-2000003</x:v>
       </x:c>
@@ -2963,8 +3049,11 @@
       <x:c r="AD29" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="30">
+      <x:c r="AE29" s="8" t="str">
+        <x:v>San Francisco Central House is a house in San Francisco, California, United States, featuring three bedrooms and one bathroom in its listed layout. Wheelchair accessibility and a kitchen are among the listed conveniences. Additional amenities include air conditioning and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" ht="76" customHeight="1">
       <x:c r="A30" t="str">
         <x:v>HA-2000004</x:v>
       </x:c>
@@ -3055,8 +3144,11 @@
       <x:c r="AD30" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="31">
+      <x:c r="AE30" s="8" t="str">
+        <x:v>For a hostel stay in Chicago, Illinois, United States, Chicago Garden Hostel has three bedrooms and three bathrooms. A kitchen and internet access make it easier to maintain everyday routines. Additional amenities include pet-friendly accommodation and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" ht="76" customHeight="1">
       <x:c r="A31" t="str">
         <x:v>HA-2000005</x:v>
       </x:c>
@@ -3147,8 +3239,11 @@
       <x:c r="AD31" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="32">
+      <x:c r="AE31" s="8" t="str">
+        <x:v>The Miami Hostel is a hostel accommodation listed in Miami, Florida, United States. Its layout includes five bedrooms and one bathroom. Breakfast is listed as included, alongside internet access. The listing also includes child-friendly facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" ht="76" customHeight="1">
       <x:c r="A32" t="str">
         <x:v>HA-2000006</x:v>
       </x:c>
@@ -3239,8 +3334,11 @@
       <x:c r="AD32" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="33">
+      <x:c r="AE32" s="8" t="str">
+        <x:v>Austin Harbor Apartment is an apartment listing in Austin, Texas, United States with one bedroom and one bathroom. The property is listed as both child-friendly and pet-friendly. Other listed amenities include air conditioning, a gym, and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" ht="76" customHeight="1">
       <x:c r="A33" t="str">
         <x:v>HA-2000007</x:v>
       </x:c>
@@ -3331,8 +3429,11 @@
       <x:c r="AD33" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="34">
+      <x:c r="AE33" s="8" t="str">
+        <x:v>Based in Houston, Texas, United States, Houston Skyline Villa is listed as a villa with four bedrooms and one bathroom. The property is listed as pet-friendly and includes parking. Other listed amenities include a hot tub, a pool, and air conditioning. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" ht="76" customHeight="1">
       <x:c r="A34" t="str">
         <x:v>HA-2000008</x:v>
       </x:c>
@@ -3423,8 +3524,11 @@
       <x:c r="AD34" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="35">
+      <x:c r="AE34" s="8" t="str">
+        <x:v>In Seattle, Washington, United States, Seattle Apartment offers an apartment stay with three bedrooms and three bathrooms. Breakfast is listed as included, and a gym offers an option to stay active. Other listed amenities include a kitchen, a hot tub, and laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" ht="76" customHeight="1">
       <x:c r="A35" t="str">
         <x:v>HA-2000009</x:v>
       </x:c>
@@ -3515,8 +3619,11 @@
       <x:c r="AD35" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="36">
+      <x:c r="AE35" s="8" t="str">
+        <x:v>Denver Grand Hostel is a hostel in Denver, Colorado, United States, featuring four bedrooms and three bathrooms in its listed layout. A gym and kitchen are listed among the property's amenities. Additional amenities include air conditioning and child-friendly facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" ht="76" customHeight="1">
       <x:c r="A36" t="str">
         <x:v>HA-2000010</x:v>
       </x:c>
@@ -3607,8 +3714,11 @@
       <x:c r="AD36" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="37">
+      <x:c r="AE36" s="8" t="str">
+        <x:v>For a house stay in Boston, Massachusetts, United States, Boston Riverside House has two bedrooms and three bathrooms. The property is listed as both child-friendly and pet-friendly. The listing also includes a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" ht="76" customHeight="1">
       <x:c r="A37" t="str">
         <x:v>HA-2000011</x:v>
       </x:c>
@@ -3699,8 +3809,11 @@
       <x:c r="AD37" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="38">
+      <x:c r="AE37" s="8" t="str">
+        <x:v>Las Vegas Central Hostel is a hostel accommodation listed in Las Vegas, Nevada, United States. Its layout includes two bedrooms and one bathroom. Wheelchair accessibility and a kitchen are among the listed conveniences. Additional amenities include child-friendly facilities and internet access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" ht="76" customHeight="1">
       <x:c r="A38" t="str">
         <x:v>HA-2000012</x:v>
       </x:c>
@@ -3791,8 +3904,11 @@
       <x:c r="AD38" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="39">
+      <x:c r="AE38" s="8" t="str">
+        <x:v>Atlanta Garden Hotel is a hotel listing in Atlanta, Georgia, United States with two bedrooms and two bathrooms. Its listed features include child-friendly facilities and a hot tub. The listing also includes a kitchen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" ht="76" customHeight="1">
       <x:c r="A39" t="str">
         <x:v>HA-2000013</x:v>
       </x:c>
@@ -3883,8 +3999,11 @@
       <x:c r="AD39" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="40">
+      <x:c r="AE39" s="8" t="str">
+        <x:v>Based in Phoenix, Arizona, United States, The Phoenix Apartment is listed as an apartment with four bedrooms and three bathrooms. The property is listed as both child-friendly and pet-friendly. Additional amenities include a kitchen and wheelchair accessibility. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" ht="76" customHeight="1">
       <x:c r="A40" t="str">
         <x:v>HA-2000014</x:v>
       </x:c>
@@ -3975,8 +4094,11 @@
       <x:c r="AD40" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="41">
+      <x:c r="AE40" s="8" t="str">
+        <x:v>In Portland, Oregon, United States, Portland Harbor Villa offers a villa stay with one bedroom and one bathroom. A kitchen and internet access make it easier to maintain everyday routines. Other listed amenities include a gym, laundry facilities, and wheelchair accessibility. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" ht="76" customHeight="1">
       <x:c r="A41" t="str">
         <x:v>HA-2000015</x:v>
       </x:c>
@@ -4067,8 +4189,11 @@
       <x:c r="AD41" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="42">
+      <x:c r="AE41" s="8" t="str">
+        <x:v>Nashville Skyline Hostel is a hostel in Nashville, Tennessee, United States, featuring four bedrooms and three bathrooms in its listed layout. The property is listed as pet-friendly and includes parking. Other listed amenities include a gym. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" ht="76" customHeight="1">
       <x:c r="A42" t="str">
         <x:v>HA-2000016</x:v>
       </x:c>
@@ -4159,8 +4284,11 @@
       <x:c r="AD42" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="43">
+      <x:c r="AE42" s="8" t="str">
+        <x:v>For a house stay in New Orleans, Louisiana, United States, New Orleans House has three bedrooms and one bathroom. A kitchen and laundry facilities make everyday routines more convenient. Other listed amenities include pet-friendly accommodation, parking, and a hot tub. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" ht="76" customHeight="1">
       <x:c r="A43" t="str">
         <x:v>HA-2000017</x:v>
       </x:c>
@@ -4251,8 +4379,11 @@
       <x:c r="AD43" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="44">
+      <x:c r="AE43" s="8" t="str">
+        <x:v>Philadelphia Grand Villa is a villa accommodation listed in Philadelphia, Pennsylvania, United States. Its layout includes five bedrooms and two bathrooms. Its listed features include wheelchair accessibility and a gym. The listing also includes internet access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" ht="76" customHeight="1">
       <x:c r="A44" t="str">
         <x:v>HA-2000018</x:v>
       </x:c>
@@ -4343,8 +4474,11 @@
       <x:c r="AD44" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="45">
+      <x:c r="AE44" s="8" t="str">
+        <x:v>Washington Riverside Villa is a villa listing in Washington, District of Columbia, United States with three bedrooms and three bathrooms. The property is listed as both child-friendly and pet-friendly. Other listed amenities include wheelchair accessibility, parking, and a hot tub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" ht="76" customHeight="1">
       <x:c r="A45" t="str">
         <x:v>HA-2000019</x:v>
       </x:c>
@@ -4435,8 +4569,11 @@
       <x:c r="AD45" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="46">
+      <x:c r="AE45" s="8" t="str">
+        <x:v>Based in Honolulu, Hawaii, United States, Honolulu Central Hotel is listed as a hotel with four bedrooms and two bathrooms. The property is listed as pet-friendly and includes parking. The listing also includes a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" ht="76" customHeight="1">
       <x:c r="A46" t="str">
         <x:v>HA-2000020</x:v>
       </x:c>
@@ -4527,8 +4664,11 @@
       <x:c r="AD46" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="47">
+      <x:c r="AE46" s="8" t="str">
+        <x:v>In Detroit, Michigan, United States, Detroit Garden Resort offers a resort stay with three bedrooms and two bathrooms. A pool and hot tub provide options for relaxing between outings. Other listed amenities include wheelchair accessibility, child-friendly facilities, air conditioning, and internet access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" ht="76" customHeight="1">
       <x:c r="A47" t="str">
         <x:v>HA-2000021</x:v>
       </x:c>
@@ -4619,8 +4759,11 @@
       <x:c r="AD47" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="48">
+      <x:c r="AE47" s="8" t="str">
+        <x:v>The Minneapolis Resort is a resort in Minneapolis, Minnesota, United States, featuring four bedrooms and two bathrooms in its listed layout. Internet access and parking add everyday convenience. Other listed amenities include laundry facilities, child-friendly facilities, and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" ht="76" customHeight="1">
       <x:c r="A48" t="str">
         <x:v>HA-2000022</x:v>
       </x:c>
@@ -4711,8 +4854,11 @@
       <x:c r="AD48" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="49">
+      <x:c r="AE48" s="8" t="str">
+        <x:v>For a house stay in Salt Lake City, Utah, United States, Salt Lake City Harbor House has one bedroom and two bathrooms. Internet access and parking add everyday convenience. Other listed amenities include child-friendly facilities, laundry facilities, and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" ht="76" customHeight="1">
       <x:c r="A49" t="str">
         <x:v>HA-2000023</x:v>
       </x:c>
@@ -4803,8 +4949,11 @@
       <x:c r="AD49" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="50">
+      <x:c r="AE49" s="8" t="str">
+        <x:v>Charlotte Skyline Hostel is a hostel accommodation listed in Charlotte, North Carolina, United States. Its layout includes two bedrooms and one bathroom. Breakfast is listed as included, alongside internet access. Other listed amenities include child-friendly facilities, wheelchair accessibility, and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" ht="76" customHeight="1">
       <x:c r="A50" t="str">
         <x:v>HA-2000024</x:v>
       </x:c>
@@ -4895,8 +5044,11 @@
       <x:c r="AD50" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="51">
+      <x:c r="AE50" s="8" t="str">
+        <x:v>Columbus Hostel is a hostel listing in Columbus, Ohio, United States with one bedroom and three bathrooms. Wheelchair accessibility and parking are included among the practical features. The listing also includes pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" ht="76" customHeight="1">
       <x:c r="A51" t="str">
         <x:v>HA-2000025</x:v>
       </x:c>
@@ -4987,8 +5139,11 @@
       <x:c r="AD51" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="52">
+      <x:c r="AE51" s="8" t="str">
+        <x:v>Based in Jersey City, New Jersey, United States, Jersey City Grand Villa is listed as a villa with one bedroom and two bathrooms. A gym and kitchen are listed among the property's amenities. Other listed amenities include laundry facilities, parking, and air conditioning. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" ht="76" customHeight="1">
       <x:c r="A52" t="str">
         <x:v>HG-3000001</x:v>
       </x:c>
@@ -5079,8 +5234,11 @@
       <x:c r="AD52" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="53">
+      <x:c r="AE52" s="8" t="str">
+        <x:v>In Toronto, Ontario, Canada, Toronto Grand Villa offers a villa stay with three bedrooms and three bathrooms. A pool and hot tub provide options for relaxing between outings. Other listed amenities include wheelchair accessibility, laundry facilities, and internet access. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" ht="76" customHeight="1">
       <x:c r="A53" t="str">
         <x:v>HG-3000002</x:v>
       </x:c>
@@ -5171,8 +5329,11 @@
       <x:c r="AD53" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="54">
+      <x:c r="AE53" s="8" t="str">
+        <x:v>Ottawa Riverside Resort is a resort in Ottawa, Ontario, Canada, featuring three bedrooms and three bathrooms in its listed layout. Breakfast is listed as included, alongside internet access. Other listed amenities include child-friendly facilities, air conditioning, and a kitchen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" ht="76" customHeight="1">
       <x:c r="A54" t="str">
         <x:v>HG-3000003</x:v>
       </x:c>
@@ -5263,8 +5424,11 @@
       <x:c r="AD54" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="55">
+      <x:c r="AE54" s="8" t="str">
+        <x:v>For a resort stay in Vancouver, British Columbia, Canada, Vancouver Central Resort has four bedrooms and three bathrooms. The property is listed as both child-friendly and pet-friendly. Additional amenities include a gym and a hot tub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" ht="76" customHeight="1">
       <x:c r="A55" t="str">
         <x:v>HG-3000004</x:v>
       </x:c>
@@ -5355,8 +5519,11 @@
       <x:c r="AD55" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="56">
+      <x:c r="AE55" s="8" t="str">
+        <x:v>Victoria Garden Villa is a villa accommodation listed in Victoria, British Columbia, Canada. Its layout includes one bedroom and two bathrooms. The property is listed as child-friendly and includes a pool. Other listed amenities include pet-friendly accommodation, internet access, laundry facilities, and a hot tub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" ht="76" customHeight="1">
       <x:c r="A56" t="str">
         <x:v>HG-3000005</x:v>
       </x:c>
@@ -5447,8 +5614,11 @@
       <x:c r="AD56" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="57">
+      <x:c r="AE56" s="8" t="str">
+        <x:v>The Montreal Villa is a villa listing in Montreal, Quebec, Canada with one bedroom and two bathrooms. Breakfast is listed as included, alongside internet access. Other listed amenities include parking, pet-friendly accommodation, child-friendly facilities, and laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" ht="76" customHeight="1">
       <x:c r="A57" t="str">
         <x:v>HG-3000006</x:v>
       </x:c>
@@ -5539,8 +5709,11 @@
       <x:c r="AD57" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="58">
+      <x:c r="AE57" s="8" t="str">
+        <x:v>Based in Quebec City, Quebec, Canada, Quebec City Harbor Resort is listed as a resort with three bedrooms and two bathrooms. A gym and kitchen are listed among the property's amenities. Other listed amenities include child-friendly facilities, internet access, air conditioning, and parking.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" ht="76" customHeight="1">
       <x:c r="A58" t="str">
         <x:v>HG-3000007</x:v>
       </x:c>
@@ -5631,8 +5804,11 @@
       <x:c r="AD58" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="59">
+      <x:c r="AE58" s="8" t="str">
+        <x:v>In Calgary, Alberta, Canada, Calgary Skyline Resort offers a resort stay with one bedroom and one bathroom. Breakfast is listed as included, alongside internet access. Additional amenities include wheelchair accessibility and a hot tub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" ht="76" customHeight="1">
       <x:c r="A59" t="str">
         <x:v>HG-3000008</x:v>
       </x:c>
@@ -5723,8 +5899,11 @@
       <x:c r="AD59" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="60">
+      <x:c r="AE59" s="8" t="str">
+        <x:v>Edmonton Hostel is a hostel in Edmonton, Alberta, Canada, featuring one bedroom and three bathrooms in its listed layout. The property is listed as pet-friendly and includes parking. The listing also includes a hot tub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" ht="76" customHeight="1">
       <x:c r="A60" t="str">
         <x:v>HG-3000009</x:v>
       </x:c>
@@ -5815,8 +5994,11 @@
       <x:c r="AD60" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="61">
+      <x:c r="AE60" s="8" t="str">
+        <x:v>For a villa stay in Winnipeg, Manitoba, Canada, Winnipeg Grand Villa has five bedrooms and one bathroom. A hot tub and gym give guests both relaxation and activity options. Additional amenities include laundry facilities and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" ht="76" customHeight="1">
       <x:c r="A61" t="str">
         <x:v>HG-3000010</x:v>
       </x:c>
@@ -5907,8 +6089,11 @@
       <x:c r="AD61" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="62">
+      <x:c r="AE61" s="8" t="str">
+        <x:v>Saskatoon Riverside Apartment is an apartment accommodation listed in Saskatoon, Saskatchewan, Canada. Its layout includes two bedrooms and one bathroom. With breakfast included and a kitchen, guests have practical choices for meals. The listing also includes laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" ht="76" customHeight="1">
       <x:c r="A62" t="str">
         <x:v>HG-3000011</x:v>
       </x:c>
@@ -5999,8 +6184,11 @@
       <x:c r="AD62" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="63">
+      <x:c r="AE62" s="8" t="str">
+        <x:v>Halifax Central Villa is a villa listing in Halifax, Nova Scotia, Canada with four bedrooms and two bathrooms. A hot tub and gym give guests both relaxation and activity options. Other listed amenities include wheelchair accessibility, a kitchen, and air conditioning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" ht="76" customHeight="1">
       <x:c r="A63" t="str">
         <x:v>HG-3000012</x:v>
       </x:c>
@@ -6091,8 +6279,11 @@
       <x:c r="AD63" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="64">
+      <x:c r="AE63" s="8" t="str">
+        <x:v>Based in Moncton, New Brunswick, Canada, Moncton Garden Hotel is listed as a hotel with five bedrooms and three bathrooms. Wheelchair accessibility and parking are included among the practical features. Other listed amenities include internet access, a hot tub, and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" ht="76" customHeight="1">
       <x:c r="A64" t="str">
         <x:v>HG-3000013</x:v>
       </x:c>
@@ -6183,8 +6374,11 @@
       <x:c r="AD64" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="65">
+      <x:c r="AE64" s="8" t="str">
+        <x:v>In St. Johns, Newfoundland and Labrador, Canada, The St. Johns Hotel offers a hotel stay with three bedrooms and three bathrooms. Air conditioning and internet access are among the listed comforts. The listing also includes laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" ht="76" customHeight="1">
       <x:c r="A65" t="str">
         <x:v>HG-3000014</x:v>
       </x:c>
@@ -6275,8 +6469,11 @@
       <x:c r="AD65" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="66">
+      <x:c r="AE65" s="8" t="str">
+        <x:v>Charlottetown Harbor Resort is a resort in Charlottetown, Prince Edward Island, Canada, featuring five bedrooms and two bathrooms in its listed layout. Wheelchair accessibility and a kitchen are among the listed conveniences. Additional amenities include a hot tub and parking.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" ht="76" customHeight="1">
       <x:c r="A66" t="str">
         <x:v>HG-3000015</x:v>
       </x:c>
@@ -6367,8 +6564,11 @@
       <x:c r="AD66" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="67">
+      <x:c r="AE66" s="8" t="str">
+        <x:v>For a villa stay in Hamilton, Ontario, Canada, Hamilton Skyline Villa has three bedrooms and three bathrooms. Breakfast is listed as included, alongside internet access. Other listed amenities include pet-friendly accommodation, a hot tub, and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" ht="76" customHeight="1">
       <x:c r="A67" t="str">
         <x:v>HG-3000016</x:v>
       </x:c>
@@ -6459,8 +6659,11 @@
       <x:c r="AD67" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="68">
+      <x:c r="AE67" s="8" t="str">
+        <x:v>London Hostel is a hostel accommodation listed in London, Ontario, Canada. Its layout includes two bedrooms and three bathrooms. A hot tub and gym give guests both relaxation and activity options. Additional amenities include wheelchair accessibility and internet access.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" ht="76" customHeight="1">
       <x:c r="A68" t="str">
         <x:v>HG-3000017</x:v>
       </x:c>
@@ -6551,8 +6754,11 @@
       <x:c r="AD68" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="69">
+      <x:c r="AE68" s="8" t="str">
+        <x:v>Kelowna Grand Resort is a resort listing in Kelowna, British Columbia, Canada with five bedrooms and three bathrooms. A hot tub and air conditioning are among the advertised comforts. Other listed amenities include laundry facilities. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" ht="76" customHeight="1">
       <x:c r="A69" t="str">
         <x:v>HG-3000018</x:v>
       </x:c>
@@ -6643,8 +6849,11 @@
       <x:c r="AD69" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="70">
+      <x:c r="AE69" s="8" t="str">
+        <x:v>Based in Banff, Alberta, Canada, Banff Riverside Hostel is listed as a hostel with three bedrooms and two bathrooms. A pool and hot tub provide options for relaxing between outings. Other listed amenities include laundry facilities, pet-friendly accommodation, and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" ht="76" customHeight="1">
       <x:c r="A70" t="str">
         <x:v>HG-3000019</x:v>
       </x:c>
@@ -6735,8 +6944,11 @@
       <x:c r="AD70" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="71">
+      <x:c r="AE70" s="8" t="str">
+        <x:v>In Gatineau, Quebec, Canada, Gatineau Central House offers a house stay with four bedrooms and one bathroom. The property is listed as pet-friendly and includes parking. Additional amenities include a pool and air conditioning. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" ht="76" customHeight="1">
       <x:c r="A71" t="str">
         <x:v>HG-3000020</x:v>
       </x:c>
@@ -6827,8 +7039,11 @@
       <x:c r="AD71" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="72">
+      <x:c r="AE71" s="8" t="str">
+        <x:v>Whitehorse Garden Villa is a villa in Whitehorse, Yukon, Canada, featuring three bedrooms and one bathroom in its listed layout. Air conditioning and internet access are among the listed comforts. The listing also includes wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" ht="76" customHeight="1">
       <x:c r="A72" t="str">
         <x:v>HG-3000021</x:v>
       </x:c>
@@ -6919,8 +7134,11 @@
       <x:c r="AD72" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="73">
+      <x:c r="AE72" s="8" t="str">
+        <x:v>For a house stay in Yellowknife, Northwest Territories, Canada, The Yellowknife House has two bedrooms and three bathrooms. A hot tub and gym give guests both relaxation and activity options. Additional amenities include child-friendly facilities and air conditioning. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" ht="76" customHeight="1">
       <x:c r="A73" t="str">
         <x:v>HG-3000022</x:v>
       </x:c>
@@ -7011,8 +7229,11 @@
       <x:c r="AD73" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="74">
+      <x:c r="AE73" s="8" t="str">
+        <x:v>Iqaluit Harbor Hostel is a hostel accommodation listed in Iqaluit, Nunavut, Canada. Its layout includes two bedrooms and three bathrooms. Laundry facilities and parking add practical convenience. Other listed amenities include pet-friendly accommodation, a gym, and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" ht="76" customHeight="1">
       <x:c r="A74" t="str">
         <x:v>HG-3000023</x:v>
       </x:c>
@@ -7103,8 +7324,11 @@
       <x:c r="AD74" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="75">
+      <x:c r="AE74" s="8" t="str">
+        <x:v>Niagara Falls Skyline Resort is a resort listing in Niagara Falls, Ontario, Canada with one bedroom and one bathroom. A pool and hot tub provide options for relaxing between outings. Other listed amenities include internet access, wheelchair accessibility, and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" ht="76" customHeight="1">
       <x:c r="A75" t="str">
         <x:v>HG-3000024</x:v>
       </x:c>
@@ -7195,8 +7419,11 @@
       <x:c r="AD75" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="76">
+      <x:c r="AE75" s="8" t="str">
+        <x:v>Based in Whistler, British Columbia, Canada, Whistler Apartment is listed as an apartment with three bedrooms and three bathrooms. A gym and kitchen are listed among the property's amenities. Additional amenities include child-friendly facilities and parking.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" ht="76" customHeight="1">
       <x:c r="A76" t="str">
         <x:v>HG-3000025</x:v>
       </x:c>
@@ -7287,8 +7514,11 @@
       <x:c r="AD76" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="77">
+      <x:c r="AE76" s="8" t="str">
+        <x:v>In Jasper, Alberta, Canada, Jasper Grand House offers a house stay with four bedrooms and three bathrooms. Wheelchair accessibility and a kitchen are among the listed conveniences. Additional amenities include air conditioning and pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" ht="76" customHeight="1">
       <x:c r="A77" t="str">
         <x:v>EP-4000001</x:v>
       </x:c>
@@ -7379,8 +7609,11 @@
       <x:c r="AD77" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="78">
+      <x:c r="AE77" s="8" t="str">
+        <x:v>London Grand Hostel is a hostel in London, England, United Kingdom, featuring three bedrooms and two bathrooms in its listed layout. The property is listed as child-friendly and includes a pool. Additional amenities include parking and a gym.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" ht="76" customHeight="1">
       <x:c r="A78" t="str">
         <x:v>EP-4000002</x:v>
       </x:c>
@@ -7471,8 +7704,11 @@
       <x:c r="AD78" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="79">
+      <x:c r="AE78" s="8" t="str">
+        <x:v>For a hostel stay in Manchester, England, United Kingdom, Manchester Riverside Hostel has three bedrooms and three bathrooms. The gym and pool offer options for exercise and downtime. The listing also includes wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" ht="76" customHeight="1">
       <x:c r="A79" t="str">
         <x:v>EP-4000003</x:v>
       </x:c>
@@ -7563,8 +7799,11 @@
       <x:c r="AD79" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="80">
+      <x:c r="AE79" s="8" t="str">
+        <x:v>Edinburgh Central Hotel is a hotel accommodation listed in Edinburgh, Scotland, United Kingdom. Its layout includes five bedrooms and one bathroom. The property is listed as both child-friendly and pet-friendly. Other listed amenities include laundry facilities, a kitchen, and air conditioning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" ht="76" customHeight="1">
       <x:c r="A80" t="str">
         <x:v>EP-4000004</x:v>
       </x:c>
@@ -7655,8 +7894,11 @@
       <x:c r="AD80" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="81">
+      <x:c r="AE80" s="8" t="str">
+        <x:v>Cardiff Garden House is a house listing in Cardiff, Wales, United Kingdom with five bedrooms and one bathroom. The property is listed as both child-friendly and pet-friendly. Other listed amenities include a pool, internet access, and wheelchair accessibility. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" ht="76" customHeight="1">
       <x:c r="A81" t="str">
         <x:v>EP-4000005</x:v>
       </x:c>
@@ -7747,8 +7989,11 @@
       <x:c r="AD81" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="82">
+      <x:c r="AE81" s="8" t="str">
+        <x:v>Based in Belfast, Northern Ireland, United Kingdom, The Belfast Resort is listed as a resort with one bedroom and one bathroom. A hot tub and air conditioning are among the advertised comforts. Additional amenities include pet-friendly accommodation and child-friendly facilities. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" ht="76" customHeight="1">
       <x:c r="A82" t="str">
         <x:v>EP-4000006</x:v>
       </x:c>
@@ -7839,8 +8084,11 @@
       <x:c r="AD82" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="83">
+      <x:c r="AE82" s="8" t="str">
+        <x:v>In Birmingham, England, United Kingdom, Birmingham Harbor Villa offers a villa stay with two bedrooms and one bathroom. Its listed features include a hot tub and breakfast included. The listing also includes wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" ht="76" customHeight="1">
       <x:c r="A83" t="str">
         <x:v>EP-4000007</x:v>
       </x:c>
@@ -7931,8 +8179,11 @@
       <x:c r="AD83" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="84">
+      <x:c r="AE83" s="8" t="str">
+        <x:v>Liverpool Skyline House is a house in Liverpool, England, United Kingdom, featuring four bedrooms and one bathroom in its listed layout. Breakfast is listed as included, and a gym offers an option to stay active. Additional amenities include wheelchair accessibility and pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" ht="76" customHeight="1">
       <x:c r="A84" t="str">
         <x:v>EP-4000008</x:v>
       </x:c>
@@ -8023,8 +8274,11 @@
       <x:c r="AD84" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="85">
+      <x:c r="AE84" s="8" t="str">
+        <x:v>For a hotel stay in Bristol, England, United Kingdom, Bristol Hotel has one bedroom and three bathrooms. Wheelchair accessibility and parking are included among the practical features. Other listed amenities include air conditioning, internet access, and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" ht="76" customHeight="1">
       <x:c r="A85" t="str">
         <x:v>EP-4000009</x:v>
       </x:c>
@@ -8115,8 +8369,11 @@
       <x:c r="AD85" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="86">
+      <x:c r="AE85" s="8" t="str">
+        <x:v>Sydney Grand House is a house accommodation listed in Sydney, New South Wales, Australia. Its layout includes two bedrooms and two bathrooms. Laundry facilities and parking add practical convenience. Other listed amenities include a hot tub, pet-friendly accommodation, a gym, and a kitchen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" ht="76" customHeight="1">
       <x:c r="A86" t="str">
         <x:v>EP-4000010</x:v>
       </x:c>
@@ -8207,8 +8464,11 @@
       <x:c r="AD86" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="87">
+      <x:c r="AE86" s="8" t="str">
+        <x:v>Melbourne Riverside Hotel is a hotel listing in Melbourne, Victoria, Australia with five bedrooms and three bathrooms. With breakfast included and a kitchen, guests have practical choices for meals. Other listed amenities include air conditioning, a gym, and a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" ht="76" customHeight="1">
       <x:c r="A87" t="str">
         <x:v>EP-4000011</x:v>
       </x:c>
@@ -8299,8 +8559,11 @@
       <x:c r="AD87" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="88">
+      <x:c r="AE87" s="8" t="str">
+        <x:v>Based in Brisbane, Queensland, Australia, Brisbane Central Resort is listed as a resort with two bedrooms and one bathroom. Its listed features include breakfast included and air conditioning. The listing also includes a pool.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" ht="76" customHeight="1">
       <x:c r="A88" t="str">
         <x:v>EP-4000012</x:v>
       </x:c>
@@ -8391,8 +8654,11 @@
       <x:c r="AD88" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="89">
+      <x:c r="AE88" s="8" t="str">
+        <x:v>In Perth, Western Australia, Australia, Perth Garden House offers a house stay with five bedrooms and two bathrooms. With breakfast included and a kitchen, guests have practical choices for meals. Additional amenities include a hot tub and pet-friendly accommodation.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" ht="76" customHeight="1">
       <x:c r="A89" t="str">
         <x:v>EP-4000013</x:v>
       </x:c>
@@ -8483,8 +8749,11 @@
       <x:c r="AD89" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="90">
+      <x:c r="AE89" s="8" t="str">
+        <x:v>The Adelaide House is a house in Adelaide, South Australia, Australia, featuring two bedrooms and three bathrooms in its listed layout. Laundry facilities and parking add practical convenience. The listing also includes a kitchen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" ht="76" customHeight="1">
       <x:c r="A90" t="str">
         <x:v>EP-4000014</x:v>
       </x:c>
@@ -8575,8 +8844,11 @@
       <x:c r="AD90" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="91">
+      <x:c r="AE90" s="8" t="str">
+        <x:v>For a hostel stay in Canberra, Australian Capital Territory, Australia, Canberra Harbor Hostel has five bedrooms and two bathrooms. Its listed features include internet access and a hot tub. The listing also includes laundry facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" ht="76" customHeight="1">
       <x:c r="A91" t="str">
         <x:v>EP-4000015</x:v>
       </x:c>
@@ -8667,8 +8939,11 @@
       <x:c r="AD91" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="92">
+      <x:c r="AE91" s="8" t="str">
+        <x:v>Hobart Skyline Resort is a resort accommodation listed in Hobart, Tasmania, Australia. Its layout includes five bedrooms and three bathrooms. With breakfast included and a kitchen, guests have practical choices for meals. Other listed amenities include laundry facilities, parking, a hot tub, and air conditioning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" ht="76" customHeight="1">
       <x:c r="A92" t="str">
         <x:v>EP-4000016</x:v>
       </x:c>
@@ -8759,8 +9034,11 @@
       <x:c r="AD92" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="93">
+      <x:c r="AE92" s="8" t="str">
+        <x:v>Munich House is a house listing in Munich, Bavaria, Germany with three bedrooms and two bathrooms. Wheelchair accessibility and parking are included among the practical features. Additional amenities include pet-friendly accommodation and a hot tub.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" ht="76" customHeight="1">
       <x:c r="A93" t="str">
         <x:v>EP-4000017</x:v>
       </x:c>
@@ -8851,8 +9129,11 @@
       <x:c r="AD93" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="94">
+      <x:c r="AE93" s="8" t="str">
+        <x:v>Based in Berlin, Germany, Berlin Grand Apartment is listed as an apartment with four bedrooms and two bathrooms. Its listed features include a hot tub and parking. Additional amenities include child-friendly facilities and a kitchen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" ht="76" customHeight="1">
       <x:c r="A94" t="str">
         <x:v>EP-4000018</x:v>
       </x:c>
@@ -8943,8 +9224,11 @@
       <x:c r="AD94" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="95">
+      <x:c r="AE94" s="8" t="str">
+        <x:v>In Hamburg, Germany, Hamburg Riverside Villa offers a villa stay with one bedroom and one bathroom. The gym and pool offer options for exercise and downtime. The listing also includes air conditioning.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" ht="76" customHeight="1">
       <x:c r="A95" t="str">
         <x:v>EP-4000019</x:v>
       </x:c>
@@ -9035,8 +9319,11 @@
       <x:c r="AD95" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="96">
+      <x:c r="AE95" s="8" t="str">
+        <x:v>Cologne Central House is a house in Cologne, North Rhine-Westphalia, Germany, featuring one bedroom and one bathroom in its listed layout. The property is listed as pet-friendly and includes parking. Other listed amenities include a kitchen, internet access, and wheelchair accessibility.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" ht="76" customHeight="1">
       <x:c r="A96" t="str">
         <x:v>EP-4000020</x:v>
       </x:c>
@@ -9127,8 +9414,11 @@
       <x:c r="AD96" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="97">
+      <x:c r="AE96" s="8" t="str">
+        <x:v>For a resort stay in Frankfurt, Hesse, Germany, Frankfurt Garden Resort has two bedrooms and one bathroom. The property is listed as both child-friendly and pet-friendly. Other listed amenities include a pool. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" ht="76" customHeight="1">
       <x:c r="A97" t="str">
         <x:v>EP-4000021</x:v>
       </x:c>
@@ -9219,8 +9509,11 @@
       <x:c r="AD97" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="98">
+      <x:c r="AE97" s="8" t="str">
+        <x:v>The Stuttgart Hotel is a hotel accommodation listed in Stuttgart, Baden-Wurttemberg, Germany. Its layout includes three bedrooms and three bathrooms. A pool and hot tub provide options for relaxing between outings. Other listed amenities include laundry facilities, wheelchair accessibility, and pet-friendly accommodation. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" ht="76" customHeight="1">
       <x:c r="A98" t="str">
         <x:v>EP-4000022</x:v>
       </x:c>
@@ -9311,8 +9604,11 @@
       <x:c r="AD98" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="99">
+      <x:c r="AE98" s="8" t="str">
+        <x:v>Dresden Harbor Resort is a resort listing in Dresden, Saxony, Germany with three bedrooms and two bathrooms. The property is listed as both child-friendly and pet-friendly. Additional amenities include air conditioning and a kitchen.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" ht="76" customHeight="1">
       <x:c r="A99" t="str">
         <x:v>EP-4000023</x:v>
       </x:c>
@@ -9403,8 +9699,11 @@
       <x:c r="AD99" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="100">
+      <x:c r="AE99" s="8" t="str">
+        <x:v>Based in Paris, Ile-de-France, France, Paris Skyline Resort is listed as a resort with two bedrooms and two bathrooms. A kitchen and internet access make it easier to maintain everyday routines. Additional amenities include child-friendly facilities and a gym. Breakfast is also included.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" ht="76" customHeight="1">
       <x:c r="A100" t="str">
         <x:v>EP-4000024</x:v>
       </x:c>
@@ -9495,8 +9794,11 @@
       <x:c r="AD100" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
       </x:c>
-    </x:row>
-    <x:row r="101">
+      <x:c r="AE100" s="8" t="str">
+        <x:v>In Nice, Provence-Alpes-Cote dAzur, France, Nice Hostel offers a hostel stay with four bedrooms and two bathrooms. Internet access and parking add everyday convenience. Additional amenities include laundry facilities and child-friendly facilities.</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="101" ht="76" customHeight="1">
       <x:c r="A101" t="str">
         <x:v>EP-4000025</x:v>
       </x:c>
@@ -9586,6 +9888,9 @@
       </x:c>
       <x:c r="AD101" t="str">
         <x:v>DEMO_SYNTHETIC_PROPERTY_AND_POLYGONS__SOURCE_LONLAT_USED_AS_LOCATION_REFERENCE</x:v>
+      </x:c>
+      <x:c r="AE101" s="8" t="str">
+        <x:v>Barcelona Grand Resort is a resort in Barcelona, Catalonia, Spain, featuring three bedrooms and one bathroom in its listed layout. A gym and kitchen are listed among the property's amenities. The listing also includes internet access.</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
@@ -9689,6 +9994,14 @@
         <x:v>Django management command must validate geometry and parse JSON/boolean/numeric columns for CSV, Excel, Parquet.</x:v>
       </x:c>
     </x:row>
+    <x:row r="12">
+      <x:c r="A12" t="str">
+        <x:v>property_description</x:v>
+      </x:c>
+      <x:c r="B12" t="str">
+        <x:v>Individual descriptive text assembled from existing property name, type, location, bedrooms, bathrooms, and listed amenities. No external verification or additional property features are implied.</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </x:worksheet>
